--- a/Cronograma FACYT.xlsx
+++ b/Cronograma FACYT.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
   <si>
     <t>Lunes</t>
   </si>
@@ -43,18 +43,6 @@
   </si>
   <si>
     <t>Actividad / Sesión</t>
-  </si>
-  <si>
-    <t>Dr. Isnel Ubaque Diaz</t>
-  </si>
-  <si>
-    <t>Hidrógeno verde, rutas de producción y principales aplicaciones en el contexto regional</t>
-  </si>
-  <si>
-    <t>Dr. José Luis Vazquez</t>
-  </si>
-  <si>
-    <t>Proyectos de Investigación e Innovación en Salud usando IA</t>
   </si>
   <si>
     <t>08:30 - 09:00</t>
@@ -65,6 +53,127 @@
   <si>
     <t>Arq Juan Manuel Bernal 
 Arq Laura Urueña, (COLOMBIA)- Workshop "Paisajes Invisibles": Territorios en Reconciliación con Sistemas Hidricos</t>
+  </si>
+  <si>
+    <t>Espacio Empresarial. Riedertech."Herramientas de diseño y proyecto eléctrico SIMARIS Suite", Paraguay</t>
+  </si>
+  <si>
+    <t>Dr. Ing. Marcelo Romero</t>
+  </si>
+  <si>
+    <t>Ingenieria de datos en Entornos industriales</t>
+  </si>
+  <si>
+    <t>09:00 - 9:30</t>
+  </si>
+  <si>
+    <t>Conferencia Inaugural</t>
+  </si>
+  <si>
+    <t>MSc. Ing. Christian Gonzalez. "Cementos LC3: Una alternativa sostenible para la construcción" (UC, PARAGUAY)</t>
+  </si>
+  <si>
+    <t>09:30 - 10:30</t>
+  </si>
+  <si>
+    <t>Presentaciones de Trabajos Científicos (Bloque Mañana I)</t>
+  </si>
+  <si>
+    <t>De la Escuela a la Universidad. Experiencias y Retos en la Robótica Educativa. Leslie Maldonado, Dulce Duro.</t>
+  </si>
+  <si>
+    <t>Visita Técnica Planta de H2-PTI-PY</t>
+  </si>
+  <si>
+    <t>Visita Técnica. Planta Solar Flotante. ITAIPU</t>
+  </si>
+  <si>
+    <t>10:30 - 11:00</t>
+  </si>
+  <si>
+    <t>Coffee Break</t>
+  </si>
+  <si>
+    <t>Visita Técnica Planta de H2 PTI-PY</t>
+  </si>
+  <si>
+    <t>11:00 - 12:00</t>
+  </si>
+  <si>
+    <t>Presentaciones de Trabajos Científicos (Bloque Mañana II)</t>
+  </si>
+  <si>
+    <t>12:00 - 13:00</t>
+  </si>
+  <si>
+    <t>Pausa / Almuerzo Libre</t>
+  </si>
+  <si>
+    <t>Reunión técnica (CyT-FACYT-ITAIPU)</t>
+  </si>
+  <si>
+    <t>13:00 – 14:00</t>
+  </si>
+  <si>
+    <t>TALLER: Tecnologias del Hidrógeno. Dr. Isnel Ubaque Diaz (30lugares), (BRASIL). Sala 21.</t>
+  </si>
+  <si>
+    <t>14:00 -15: 00</t>
+  </si>
+  <si>
+    <t>Presentaciones de Trabajos Científicos (Bloque Tarde I)</t>
+  </si>
+  <si>
+    <t>Espacio Empresarial.</t>
+  </si>
+  <si>
+    <t>Arq Juan Manuel Bernal 
+Arq Laura Urueña, Workshop "Paisajes Invisibles": Territorios en Reconciliación con Sistemas Hidricos. (COLOMBIA)</t>
+  </si>
+  <si>
+    <t>TALLER: Introducción a Dinamica de Fluidos Computacional. Dr. Vinicius Poletto, (UTFPR, BRASIL)</t>
+  </si>
+  <si>
+    <t>15:00 – 16:00</t>
+  </si>
+  <si>
+    <t>Presentaciones de Trabajos Científicos (Bloque Tarde II)</t>
+  </si>
+  <si>
+    <t>Espacio Empresarial</t>
+  </si>
+  <si>
+    <t>16:00 - 17:00</t>
+  </si>
+  <si>
+    <t>Apertura de Exposición de Pósteres</t>
+  </si>
+  <si>
+    <t>Ing. Lucas Ricardo. "Impresión 3D: Herramienta para la presentación de proyectos". (Anga3D, PARAGUAY)</t>
+  </si>
+  <si>
+    <t>BLOQUE DE ENERGIA: Conferencia "Politica Energética en la UC". Ing. Sergio Oddone, (MADES, PARAGUAY).
+16:00 Hs. Presentación sobre la Política Energética de la UC y Proyecto Piloto “Sistema de Gestión de Energía – ISO 50001 en la FCYT” (Grupo de investigación en Energía, FCYT UC Asunción).
+17:00 Hs. Presentación sobre Normas Técnicas de Eficiencia Energética (INTN, CTN 51).
+18:00 Hs. Presentación sobre Eficiencia Energética en el Protocolo de Montreal y Enmienda de Kigali (Ozono/DGA. MADES).</t>
+  </si>
+  <si>
+    <t>Ing. José Duarte. "Interacción suelo-estructura aplicada: una herramienta computacional para el análisis de fundaciones superficiales y profundas en diferentes tipos de estratos", (JD Ingeniería y Construcción,PARAGUAY)</t>
+  </si>
+  <si>
+    <t>Hidrógeno verde, rutas de producción y principales aplicaciones en el contexto regional. Dr. Isnel Ubaque Diaz, (SENAI, BRASIL)</t>
+  </si>
+  <si>
+    <t>17:00 - 18:00</t>
+  </si>
+  <si>
+    <t>Conferencia: "Proyectos de Investigación e Innovación en Salud usando IA" Dr. José Luis Vazquez,  (FPUNA, PARAGUAY)</t>
+  </si>
+  <si>
+    <t>Ing. Paulo Melgarejo. "De Corea del Sur al Paraguay: matricería y manufactura avanzada, el camino hacia la Industria 4.0"  (PTI, PARAGUAY)</t>
+  </si>
+  <si>
+    <t>Panel WIE (Women in Engineering). Dra. Ing. Gabriela Cáceres, Ing. Yanine Mendoza, Ing. Verónica Lambaré</t>
   </si>
   <si>
     <r>
@@ -85,121 +194,22 @@
     </r>
   </si>
   <si>
-    <t>Espacio Empresarial. Riedertech."Herramientas de diseño y proyecto eléctrico SIMARIS Suite", Paraguay</t>
-  </si>
-  <si>
-    <t>Dr. Ing. Marcelo Romero</t>
-  </si>
-  <si>
-    <t>Ingenieria de datos en Entornos industriales</t>
-  </si>
-  <si>
-    <t>09:00 - 9:30</t>
-  </si>
-  <si>
-    <t>Conferencia Inaugural</t>
-  </si>
-  <si>
-    <t>MSc. Ing. Christian Gonzalez, UC (PARAGUAY)</t>
-  </si>
-  <si>
-    <t>09:30 - 10:30</t>
-  </si>
-  <si>
-    <t>Presentaciones de Trabajos Científicos (Bloque Mañana I)</t>
-  </si>
-  <si>
-    <t>Visita Técnica. Planta Solar Flotante. ITAIPU</t>
-  </si>
-  <si>
-    <t>Visita Técnica Planta de H2-PTI-PY</t>
-  </si>
-  <si>
-    <t>Dra. Gabriela Cáceres</t>
-  </si>
-  <si>
-    <t>10:30 - 11:00</t>
-  </si>
-  <si>
-    <t>Coffee Break</t>
-  </si>
-  <si>
-    <t>Visita Técnica Planta de H2 PTI-PY</t>
-  </si>
-  <si>
-    <t>Ing. Sergio Oddone</t>
-  </si>
-  <si>
-    <t>11:00 - 12:00</t>
-  </si>
-  <si>
-    <t>Presentaciones de Trabajos Científicos (Bloque Mañana II)</t>
-  </si>
-  <si>
-    <t>Ministro Presidente Dr. Benjamin Barán</t>
-  </si>
-  <si>
-    <t>"La Ciencia en Paraguay"</t>
-  </si>
-  <si>
-    <t>12:00 - 13:00</t>
-  </si>
-  <si>
-    <t>Pausa / Almuerzo Libre</t>
-  </si>
-  <si>
-    <t>13:00 – 14:00</t>
-  </si>
-  <si>
-    <t>14:00 -15: 00</t>
-  </si>
-  <si>
-    <t>Presentaciones de Trabajos Científicos (Bloque Tarde I)</t>
-  </si>
-  <si>
-    <t>Espacio Empresarial.</t>
-  </si>
-  <si>
-    <t>TALLER: Introducción a Dinamica de Fluidos Computacional. Dr. Vinicius Poletto, (UTFPR, BRASIL)</t>
-  </si>
-  <si>
-    <t>TALLER: Tecnologias del Hidrógeno. Dr. Isnel Ubaque Diaz (30lugares), (BRASIL). Sala 21.</t>
-  </si>
-  <si>
-    <t>15:00 – 16:00</t>
-  </si>
-  <si>
-    <t>Presentaciones de Trabajos Científicos (Bloque Tarde II)</t>
-  </si>
-  <si>
-    <t>Espacio Empresarial</t>
-  </si>
-  <si>
-    <t>16:00 - 17:00</t>
-  </si>
-  <si>
-    <t>Apertura de Exposición de Pósteres</t>
-  </si>
-  <si>
-    <t>Ing. Lucas Ricardo, FPTI. "Impresión 3D: Herramienta para la presentación de proyectos". (PARAGUAY)</t>
-  </si>
-  <si>
-    <t>BLOQUE DE ENERGIA: Conferencia "Politica Energética en la UC". Ing. Sergio Oddone, (MADES, PARAGUAY).</t>
-  </si>
-  <si>
-    <t>Ing. José Duarte. JD Ingeniería y Construcción. "Interacción suelo-estructura aplicada: una herramienta computacional para el análisis de fundaciones superficiales y profundas en diferentes tipos de estratos", (PARAGUAY)</t>
-  </si>
-  <si>
-    <t>Hidrógeno verde, rutas de producción y principales aplicaciones en el contexto regional. Dr. Isnel Ubaque Diaz, (SENAI, BRASIL)</t>
-  </si>
-  <si>
-    <t>17:00 - 18:00</t>
-  </si>
-  <si>
-    <t>Conferencia: "Proyectos de Investigación e Innovación en Salud usando IA" Dr. José Luis Vazquez, FPUNA (PARAGUAY)</t>
-  </si>
-  <si>
-    <t>Ing. Paulo Melgarejo, FPTI. (PARAGUAY)</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve">Visita Técnica Obra Civil OTIFF CELL SHOPP. </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>(A confirmar)</t>
+    </r>
   </si>
   <si>
     <t>Disertación Magistral. "La Ciencia en Paraguay" - Dr. Benjamin Barán (Ministro Presidente, CONACYT, PARAGUAY)</t>
@@ -270,7 +280,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -291,12 +301,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB6D7A8"/>
-        <bgColor rgb="FFB6D7A8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEAD1DC"/>
         <bgColor rgb="FFEAD1DC"/>
       </patternFill>
@@ -309,8 +313,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB6D7A8"/>
+        <bgColor rgb="FFB6D7A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCFE2F3"/>
         <bgColor rgb="FFCFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -320,7 +336,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border/>
     <border>
       <left style="medium">
@@ -403,11 +419,27 @@
       </right>
       <bottom/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -423,32 +455,44 @@
     <xf borderId="4" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="6" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="3" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="3" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="3" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -460,14 +504,14 @@
     <xf borderId="3" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -685,7 +729,8 @@
     <col customWidth="1" min="1" max="1" width="14.71"/>
     <col customWidth="1" min="2" max="2" width="47.57"/>
     <col customWidth="1" min="3" max="3" width="40.71"/>
-    <col customWidth="1" min="4" max="5" width="27.86"/>
+    <col customWidth="1" min="4" max="4" width="32.14"/>
+    <col customWidth="1" min="5" max="5" width="27.86"/>
     <col customWidth="1" min="6" max="7" width="27.29"/>
     <col customWidth="1" min="8" max="10" width="28.57"/>
     <col customWidth="1" min="11" max="11" width="38.57"/>
@@ -752,12 +797,8 @@
       <c r="I2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4"/>
@@ -769,53 +810,47 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
     </row>
     <row r="4" ht="29.25" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E4" s="7"/>
       <c r="F4" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>17</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" ht="32.25" customHeight="1">
-      <c r="A5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>22</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -828,242 +863,245 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="D6" s="11"/>
       <c r="E6" s="12"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>26</v>
+      <c r="G6" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>22</v>
       </c>
       <c r="I6" s="11"/>
-      <c r="J6" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="J6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="13"/>
+        <v>24</v>
+      </c>
+      <c r="C7" s="15"/>
       <c r="D7" s="11"/>
       <c r="E7" s="5"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="15" t="s">
-        <v>30</v>
+      <c r="H7" s="14" t="s">
+        <v>22</v>
       </c>
       <c r="I7" s="11"/>
-      <c r="J7" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="J7" s="2"/>
     </row>
     <row r="8" ht="39.75" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="13"/>
+        <v>27</v>
+      </c>
+      <c r="C8" s="15"/>
       <c r="D8" s="16"/>
       <c r="E8" s="5"/>
       <c r="F8" s="16"/>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="15" t="s">
-        <v>30</v>
+      <c r="H8" s="14" t="s">
+        <v>22</v>
       </c>
       <c r="I8" s="16"/>
-      <c r="J8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
     </row>
     <row r="9" ht="28.5" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
+      <c r="H9" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="18"/>
+      <c r="J9" s="19"/>
     </row>
     <row r="10" ht="31.5" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
+        <v>29</v>
+      </c>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="21" t="s">
+        <v>32</v>
+      </c>
       <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="19"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>41</v>
+        <v>34</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>35</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>42</v>
+        <v>36</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>43</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="G11" s="11"/>
       <c r="H11" s="5"/>
       <c r="I11" s="6" t="s">
-        <v>15</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="J11" s="19"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>46</v>
+        <v>39</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>40</v>
       </c>
       <c r="D12" s="11"/>
-      <c r="E12" s="19" t="s">
-        <v>42</v>
+      <c r="E12" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="F12" s="11"/>
-      <c r="G12" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" s="17"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="20"/>
       <c r="I12" s="11"/>
     </row>
     <row r="13" ht="58.5" customHeight="1">
-      <c r="A13" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>48</v>
+      <c r="A13" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>42</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="5"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="22" t="s">
-        <v>50</v>
+      <c r="G13" s="21" t="s">
+        <v>44</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="11"/>
     </row>
     <row r="14" ht="102.75" customHeight="1">
       <c r="A14" s="12"/>
-      <c r="B14" s="21" t="s">
-        <v>48</v>
+      <c r="B14" s="25" t="s">
+        <v>42</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D14" s="16"/>
-      <c r="E14" s="21"/>
+      <c r="E14" s="25"/>
       <c r="F14" s="16"/>
       <c r="G14" s="11"/>
-      <c r="H14" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="16"/>
+      <c r="H14" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="12"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="17" t="s">
         <v>53</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="23" t="s">
-        <v>56</v>
       </c>
       <c r="I15" s="5"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="I16" s="5"/>
     </row>
     <row r="17" ht="56.25" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B17" s="5"/>
-      <c r="C17" s="24" t="s">
-        <v>59</v>
+      <c r="C17" s="27" t="s">
+        <v>56</v>
       </c>
       <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
+      <c r="E17" s="28"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1"/>
@@ -2050,18 +2088,21 @@
     <row r="999" ht="14.25" customHeight="1"/>
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="22">
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="I4:I8"/>
     <mergeCell ref="I11:I14"/>
-    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="G13:G16"/>
+    <mergeCell ref="G10:G12"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E6"/>
     <mergeCell ref="D11:D14"/>
     <mergeCell ref="F11:F14"/>
     <mergeCell ref="A13:A14"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
